--- a/Quina_scraper_surface.xlsx
+++ b/Quina_scraper_surface.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Quina_valleys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE907B8-AEE4-4307-8423-30A8E8895E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B763B2EB-58F0-45C1-B14A-1C125F62B8BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{51F75AC8-9BCC-468F-8814-35286D6AD1E7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{51F75AC8-9BCC-468F-8814-35286D6AD1E7}"/>
   </bookViews>
   <sheets>
     <sheet name="Quina scraper" sheetId="5" r:id="rId1"/>
@@ -1243,7 +1243,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="0.00_);[Red]\(0.00\)"/>
+    <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -1363,10 +1363,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1378,7 +1378,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1727,25 +1727,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C3B0A72-F028-47A8-9FE2-6569D238CC68}">
   <dimension ref="A1:AW167"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.6640625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="14.625" style="7" customWidth="1"/>
     <col min="2" max="2" width="13" style="6" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="23.6640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="8.88671875" style="7"/>
-    <col min="6" max="6" width="8.88671875" style="6"/>
-    <col min="7" max="7" width="11.6640625" style="6" customWidth="1"/>
-    <col min="8" max="23" width="8.88671875" style="6"/>
+    <col min="3" max="3" width="11.375" style="6" customWidth="1"/>
+    <col min="4" max="4" width="23.625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="8.875" style="7"/>
+    <col min="6" max="6" width="8.875" style="6"/>
+    <col min="7" max="7" width="11.625" style="6" customWidth="1"/>
+    <col min="8" max="23" width="8.875" style="6"/>
     <col min="24" max="24" width="12" style="6" customWidth="1"/>
-    <col min="25" max="43" width="8.88671875" style="6"/>
-    <col min="44" max="45" width="14.33203125" style="6" customWidth="1"/>
-    <col min="46" max="46" width="7.21875" style="6" customWidth="1"/>
-    <col min="47" max="48" width="11.88671875" style="6" customWidth="1"/>
-    <col min="49" max="16384" width="8.88671875" style="6"/>
+    <col min="25" max="43" width="8.875" style="6"/>
+    <col min="44" max="45" width="14.375" style="6" customWidth="1"/>
+    <col min="46" max="46" width="7.25" style="6" customWidth="1"/>
+    <col min="47" max="48" width="11.875" style="6" customWidth="1"/>
+    <col min="49" max="16384" width="8.875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" s="4" customFormat="1" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:49" s="4" customFormat="1" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>266</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="2" spans="1:49" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:49" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>0.44768489215638541</v>
       </c>
     </row>
-    <row r="3" spans="1:49" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:49" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>0.24059375946682823</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:49" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>0.29601020480476226</v>
       </c>
     </row>
-    <row r="5" spans="1:49" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -2286,7 +2286,7 @@
         <v>0.68110172245693845</v>
       </c>
     </row>
-    <row r="6" spans="1:49" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:49" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>4</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>0.49296629337452424</v>
       </c>
     </row>
-    <row r="7" spans="1:49" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:49" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>5</v>
       </c>
@@ -2480,7 +2480,7 @@
         <v>0.18332437319779094</v>
       </c>
     </row>
-    <row r="8" spans="1:49" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:49" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>0.57495418448381197</v>
       </c>
     </row>
-    <row r="9" spans="1:49" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:49" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>0.39954038082731452</v>
       </c>
     </row>
-    <row r="10" spans="1:49" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:49" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>0.46083191182259547</v>
       </c>
     </row>
-    <row r="11" spans="1:49" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:49" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>9</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>0.58687742320310154</v>
       </c>
     </row>
-    <row r="12" spans="1:49" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:49" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>10</v>
       </c>
@@ -3044,7 +3044,7 @@
         <v>0.77749891821722217</v>
       </c>
     </row>
-    <row r="13" spans="1:49" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:49" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>11</v>
       </c>
@@ -3160,7 +3160,7 @@
         <v>0.55119502192052028</v>
       </c>
     </row>
-    <row r="14" spans="1:49" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:49" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>12</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>0.30535372848948378</v>
       </c>
     </row>
-    <row r="15" spans="1:49" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:49" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>13</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>0.29572307054515301</v>
       </c>
     </row>
-    <row r="16" spans="1:49" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:49" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>14</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>0.80715282855813331</v>
       </c>
     </row>
-    <row r="17" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>15</v>
       </c>
@@ -3584,7 +3584,7 @@
         <v>0.56736938588450958</v>
       </c>
     </row>
-    <row r="18" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>16</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>0.63886955311151317</v>
       </c>
     </row>
-    <row r="19" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>17</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>0.25119766715267661</v>
       </c>
     </row>
-    <row r="20" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>18</v>
       </c>
@@ -3894,7 +3894,7 @@
         <v>0.31978798586572438</v>
       </c>
     </row>
-    <row r="21" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>19</v>
       </c>
@@ -3985,7 +3985,7 @@
         <v>0.28067111582361376</v>
       </c>
     </row>
-    <row r="22" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>20</v>
       </c>
@@ -4076,7 +4076,7 @@
         <v>0.42258487780875842</v>
       </c>
     </row>
-    <row r="23" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>21</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>0.5112218023588686</v>
       </c>
     </row>
-    <row r="24" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>22</v>
       </c>
@@ -4283,7 +4283,7 @@
         <v>0.28023998451712795</v>
       </c>
     </row>
-    <row r="25" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>23</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>0.55756703529768215</v>
       </c>
     </row>
-    <row r="26" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>24</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>0.35946364105208867</v>
       </c>
     </row>
-    <row r="27" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>25</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>0.23941760112722366</v>
       </c>
     </row>
-    <row r="28" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>26</v>
       </c>
@@ -4682,7 +4682,7 @@
         <v>0.20040048479738631</v>
       </c>
     </row>
-    <row r="29" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>27</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>0.26794674516625411</v>
       </c>
     </row>
-    <row r="30" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>28</v>
       </c>
@@ -4874,7 +4874,7 @@
         <v>0.32855766411126475</v>
       </c>
     </row>
-    <row r="31" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>29</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>0.53177151882074225</v>
       </c>
     </row>
-    <row r="32" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
         <v>30</v>
       </c>
@@ -5068,7 +5068,7 @@
         <v>0.27692926045016075</v>
       </c>
     </row>
-    <row r="33" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>31</v>
       </c>
@@ -5196,7 +5196,7 @@
         <v>0.44969962811099456</v>
       </c>
     </row>
-    <row r="34" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>32</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>0.44697701371450643</v>
       </c>
     </row>
-    <row r="35" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>33</v>
       </c>
@@ -5390,7 +5390,7 @@
         <v>0.38458188153310108</v>
       </c>
     </row>
-    <row r="36" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>34</v>
       </c>
@@ -5481,7 +5481,7 @@
         <v>0.37956339990710636</v>
       </c>
     </row>
-    <row r="37" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
         <v>35</v>
       </c>
@@ -5609,7 +5609,7 @@
         <v>0.54756743737957614</v>
       </c>
     </row>
-    <row r="38" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>36</v>
       </c>
@@ -5737,7 +5737,7 @@
         <v>0.65683510446034843</v>
       </c>
     </row>
-    <row r="39" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>37</v>
       </c>
@@ -5828,7 +5828,7 @@
         <v>0.37112517430011799</v>
       </c>
     </row>
-    <row r="40" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>38</v>
       </c>
@@ -5917,7 +5917,7 @@
         <v>0.50183823529411753</v>
       </c>
     </row>
-    <row r="41" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>39</v>
       </c>
@@ -6008,7 +6008,7 @@
         <v>0.4890029325513196</v>
       </c>
     </row>
-    <row r="42" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>40</v>
       </c>
@@ -6099,7 +6099,7 @@
         <v>0.62040816326530612</v>
       </c>
     </row>
-    <row r="43" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
         <v>41</v>
       </c>
@@ -6200,7 +6200,7 @@
         <v>0.20633981903128507</v>
       </c>
     </row>
-    <row r="44" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>42</v>
       </c>
@@ -6316,7 +6316,7 @@
         <v>0.71446742356432835</v>
       </c>
     </row>
-    <row r="45" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>43</v>
       </c>
@@ -6419,7 +6419,7 @@
         <v>0.51815799326095091</v>
       </c>
     </row>
-    <row r="46" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
         <v>44</v>
       </c>
@@ -6508,7 +6508,7 @@
         <v>0.55231774861533856</v>
       </c>
     </row>
-    <row r="47" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
         <v>267</v>
       </c>
@@ -6599,7 +6599,7 @@
         <v>0.37745041178517569</v>
       </c>
     </row>
-    <row r="48" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
         <v>45</v>
       </c>
@@ -6688,7 +6688,7 @@
         <v>0.21891172185097724</v>
       </c>
     </row>
-    <row r="49" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
         <v>46</v>
       </c>
@@ -6791,7 +6791,7 @@
         <v>0.25638674978608972</v>
       </c>
     </row>
-    <row r="50" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
         <v>47</v>
       </c>
@@ -6917,7 +6917,7 @@
         <v>0.68328752781049606</v>
       </c>
     </row>
-    <row r="51" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
         <v>48</v>
       </c>
@@ -7031,7 +7031,7 @@
         <v>0.8494141750432167</v>
       </c>
     </row>
-    <row r="52" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
         <v>49</v>
       </c>
@@ -7147,7 +7147,7 @@
         <v>0.67330611344074143</v>
       </c>
     </row>
-    <row r="53" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
         <v>50</v>
       </c>
@@ -7275,7 +7275,7 @@
         <v>0.58018073211824173</v>
       </c>
     </row>
-    <row r="54" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
         <v>51</v>
       </c>
@@ -7403,7 +7403,7 @@
         <v>0.41290093921672877</v>
       </c>
     </row>
-    <row r="55" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>52</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>0.24310363776239147</v>
       </c>
     </row>
-    <row r="56" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
         <v>53</v>
       </c>
@@ -7620,7 +7620,7 @@
         <v>0.65492451473759894</v>
       </c>
     </row>
-    <row r="57" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
         <v>54</v>
       </c>
@@ -7711,7 +7711,7 @@
         <v>0.55272348508057112</v>
       </c>
     </row>
-    <row r="58" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
         <v>55</v>
       </c>
@@ -7802,7 +7802,7 @@
         <v>0.30976645435244154</v>
       </c>
     </row>
-    <row r="59" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
         <v>56</v>
       </c>
@@ -7916,7 +7916,7 @@
         <v>0.44475500541897212</v>
       </c>
     </row>
-    <row r="60" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
         <v>57</v>
       </c>
@@ -8030,7 +8030,7 @@
         <v>0.46598082768295529</v>
       </c>
     </row>
-    <row r="61" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
         <v>58</v>
       </c>
@@ -8156,7 +8156,7 @@
         <v>0.50241976566479873</v>
       </c>
     </row>
-    <row r="62" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
         <v>59</v>
       </c>
@@ -8247,7 +8247,7 @@
         <v>0.47213622291021667</v>
       </c>
     </row>
-    <row r="63" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>60</v>
       </c>
@@ -8350,7 +8350,7 @@
         <v>0.42561683599419442</v>
       </c>
     </row>
-    <row r="64" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A64" s="5" t="s">
         <v>61</v>
       </c>
@@ -8478,7 +8478,7 @@
         <v>0.6841032075915614</v>
       </c>
     </row>
-    <row r="65" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A65" s="5" t="s">
         <v>62</v>
       </c>
@@ -8569,7 +8569,7 @@
         <v>0.27379592933431851</v>
       </c>
     </row>
-    <row r="66" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A66" s="5" t="s">
         <v>63</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>0.57319042725003677</v>
       </c>
     </row>
-    <row r="67" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
         <v>64</v>
       </c>
@@ -8776,7 +8776,7 @@
         <v>0.3850237100997948</v>
       </c>
     </row>
-    <row r="68" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A68" s="5" t="s">
         <v>65</v>
       </c>
@@ -8887,7 +8887,7 @@
         <v>0.69454949944382649</v>
       </c>
     </row>
-    <row r="69" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A69" s="5" t="s">
         <v>66</v>
       </c>
@@ -8976,7 +8976,7 @@
         <v>0.32095179863446449</v>
       </c>
     </row>
-    <row r="70" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A70" s="5" t="s">
         <v>67</v>
       </c>
@@ -9090,7 +9090,7 @@
         <v>0.61510509440684003</v>
       </c>
     </row>
-    <row r="71" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A71" s="5" t="s">
         <v>68</v>
       </c>
@@ -9179,7 +9179,7 @@
         <v>0.24159514438806964</v>
       </c>
     </row>
-    <row r="72" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A72" s="5" t="s">
         <v>69</v>
       </c>
@@ -9293,7 +9293,7 @@
         <v>0.46581699799127241</v>
       </c>
     </row>
-    <row r="73" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A73" s="5" t="s">
         <v>70</v>
       </c>
@@ -9384,7 +9384,7 @@
         <v>0.39812881129396044</v>
       </c>
     </row>
-    <row r="74" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
         <v>71</v>
       </c>
@@ -9500,7 +9500,7 @@
         <v>0.51642664266426641</v>
       </c>
     </row>
-    <row r="75" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A75" s="5" t="s">
         <v>72</v>
       </c>
@@ -9589,7 +9589,7 @@
         <v>0.31170419394288174</v>
       </c>
     </row>
-    <row r="76" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A76" s="5" t="s">
         <v>73</v>
       </c>
@@ -9692,7 +9692,7 @@
         <v>0.35033259423503321</v>
       </c>
     </row>
-    <row r="77" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A77" s="5" t="s">
         <v>74</v>
       </c>
@@ -9818,7 +9818,7 @@
         <v>0.63176514399205552</v>
       </c>
     </row>
-    <row r="78" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A78" s="5" t="s">
         <v>75</v>
       </c>
@@ -9946,7 +9946,7 @@
         <v>0.45588452997779427</v>
       </c>
     </row>
-    <row r="79" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A79" s="5" t="s">
         <v>76</v>
       </c>
@@ -10037,7 +10037,7 @@
         <v>0.45422559036470661</v>
       </c>
     </row>
-    <row r="80" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A80" s="5" t="s">
         <v>77</v>
       </c>
@@ -10126,7 +10126,7 @@
         <v>0.34516285853184253</v>
       </c>
     </row>
-    <row r="81" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A81" s="5" t="s">
         <v>78</v>
       </c>
@@ -10229,7 +10229,7 @@
         <v>0.53641173012866561</v>
       </c>
     </row>
-    <row r="82" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A82" s="5" t="s">
         <v>79</v>
       </c>
@@ -10343,7 +10343,7 @@
         <v>0.61512463033375597</v>
       </c>
     </row>
-    <row r="83" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A83" s="5" t="s">
         <v>80</v>
       </c>
@@ -10457,7 +10457,7 @@
         <v>0.62733163165128614</v>
       </c>
     </row>
-    <row r="84" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A84" s="5" t="s">
         <v>81</v>
       </c>
@@ -10548,7 +10548,7 @@
         <v>0.36597688421344043</v>
       </c>
     </row>
-    <row r="85" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
         <v>82</v>
       </c>
@@ -10639,7 +10639,7 @@
         <v>0.51678108314263915</v>
       </c>
     </row>
-    <row r="86" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A86" s="5" t="s">
         <v>83</v>
       </c>
@@ -10730,7 +10730,7 @@
         <v>0.40853658536585358</v>
       </c>
     </row>
-    <row r="87" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A87" s="5" t="s">
         <v>84</v>
       </c>
@@ -10844,7 +10844,7 @@
         <v>0.54246597150362186</v>
       </c>
     </row>
-    <row r="88" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A88" s="5" t="s">
         <v>85</v>
       </c>
@@ -10945,7 +10945,7 @@
         <v>0.35449589400317438</v>
       </c>
     </row>
-    <row r="89" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A89" s="5" t="s">
         <v>86</v>
       </c>
@@ -11034,7 +11034,7 @@
         <v>0.51825414528961256</v>
       </c>
     </row>
-    <row r="90" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A90" s="5" t="s">
         <v>87</v>
       </c>
@@ -11125,7 +11125,7 @@
         <v>0.36686227764533286</v>
       </c>
     </row>
-    <row r="91" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A91" s="5" t="s">
         <v>88</v>
       </c>
@@ -11228,7 +11228,7 @@
         <v>0.3273126434487576</v>
       </c>
     </row>
-    <row r="92" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A92" s="5" t="s">
         <v>89</v>
       </c>
@@ -11319,7 +11319,7 @@
         <v>0.29720757664518643</v>
       </c>
     </row>
-    <row r="93" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A93" s="5" t="s">
         <v>90</v>
       </c>
@@ -11408,7 +11408,7 @@
         <v>0.29029709228824274</v>
       </c>
     </row>
-    <row r="94" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A94" s="5" t="s">
         <v>91</v>
       </c>
@@ -11497,7 +11497,7 @@
         <v>0.2894876794894522</v>
       </c>
     </row>
-    <row r="95" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A95" s="5" t="s">
         <v>92</v>
       </c>
@@ -11588,7 +11588,7 @@
         <v>0.49879830618395454</v>
       </c>
     </row>
-    <row r="96" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A96" s="5" t="s">
         <v>93</v>
       </c>
@@ -11679,7 +11679,7 @@
         <v>0.33757505152791467</v>
       </c>
     </row>
-    <row r="97" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A97" s="5" t="s">
         <v>94</v>
       </c>
@@ -11782,7 +11782,7 @@
         <v>0.32501462273347642</v>
       </c>
     </row>
-    <row r="98" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A98" s="5" t="s">
         <v>95</v>
       </c>
@@ -11896,7 +11896,7 @@
         <v>0.40154810644831113</v>
       </c>
     </row>
-    <row r="99" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A99" s="5" t="s">
         <v>96</v>
       </c>
@@ -12024,7 +12024,7 @@
         <v>0.40531097134870719</v>
       </c>
     </row>
-    <row r="100" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A100" s="5" t="s">
         <v>97</v>
       </c>
@@ -12113,7 +12113,7 @@
         <v>0.22079660827847811</v>
       </c>
     </row>
-    <row r="101" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A101" s="5" t="s">
         <v>98</v>
       </c>
@@ -12202,7 +12202,7 @@
         <v>0.36497267416294993</v>
       </c>
     </row>
-    <row r="102" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A102" s="5" t="s">
         <v>99</v>
       </c>
@@ -12293,7 +12293,7 @@
         <v>0.53216695826043492</v>
       </c>
     </row>
-    <row r="103" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A103" s="5" t="s">
         <v>268</v>
       </c>
@@ -12382,7 +12382,7 @@
         <v>0.36326094349706067</v>
       </c>
     </row>
-    <row r="104" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
         <v>100</v>
       </c>
@@ -12498,7 +12498,7 @@
         <v>0.40720104878733965</v>
       </c>
     </row>
-    <row r="105" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A105" s="5" t="s">
         <v>101</v>
       </c>
@@ -12601,7 +12601,7 @@
         <v>0.22669163223140495</v>
       </c>
     </row>
-    <row r="106" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A106" s="5" t="s">
         <v>102</v>
       </c>
@@ -12717,7 +12717,7 @@
         <v>0.45102734005234146</v>
       </c>
     </row>
-    <row r="107" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A107" s="5" t="s">
         <v>103</v>
       </c>
@@ -12831,7 +12831,7 @@
         <v>0.49172017573504567</v>
       </c>
     </row>
-    <row r="108" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A108" s="5" t="s">
         <v>104</v>
       </c>
@@ -12934,7 +12934,7 @@
         <v>0.36163895486935865</v>
       </c>
     </row>
-    <row r="109" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A109" s="5" t="s">
         <v>105</v>
       </c>
@@ -13037,7 +13037,7 @@
         <v>0.34483245149911812</v>
       </c>
     </row>
-    <row r="110" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A110" s="5" t="s">
         <v>106</v>
       </c>
@@ -13151,7 +13151,7 @@
         <v>0.52398928397467115</v>
       </c>
     </row>
-    <row r="111" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A111" s="5" t="s">
         <v>107</v>
       </c>
@@ -13240,7 +13240,7 @@
         <v>0.40484593457309626</v>
       </c>
     </row>
-    <row r="112" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A112" s="5" t="s">
         <v>108</v>
       </c>
@@ -13329,7 +13329,7 @@
         <v>0.27257151370679383</v>
       </c>
     </row>
-    <row r="113" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A113" s="5" t="s">
         <v>109</v>
       </c>
@@ -13420,7 +13420,7 @@
         <v>0.22462747423826823</v>
       </c>
     </row>
-    <row r="114" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A114" s="5" t="s">
         <v>110</v>
       </c>
@@ -13534,7 +13534,7 @@
         <v>0.76703368581707199</v>
       </c>
     </row>
-    <row r="115" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A115" s="5" t="s">
         <v>111</v>
       </c>
@@ -13625,7 +13625,7 @@
         <v>0.3341870709968241</v>
       </c>
     </row>
-    <row r="116" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A116" s="5" t="s">
         <v>112</v>
       </c>
@@ -13714,7 +13714,7 @@
         <v>0.48897924245666602</v>
       </c>
     </row>
-    <row r="117" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A117" s="5" t="s">
         <v>113</v>
       </c>
@@ -13840,7 +13840,7 @@
         <v>0.54451514657094691</v>
       </c>
     </row>
-    <row r="118" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A118" s="5" t="s">
         <v>114</v>
       </c>
@@ -13943,7 +13943,7 @@
         <v>0.23800296363843609</v>
       </c>
     </row>
-    <row r="119" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A119" s="5" t="s">
         <v>115</v>
       </c>
@@ -14046,7 +14046,7 @@
         <v>0.26668637304167903</v>
       </c>
     </row>
-    <row r="120" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A120" s="5" t="s">
         <v>116</v>
       </c>
@@ -14174,7 +14174,7 @@
         <v>0.47181276021154495</v>
       </c>
     </row>
-    <row r="121" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A121" s="5" t="s">
         <v>117</v>
       </c>
@@ -14277,7 +14277,7 @@
         <v>0.39971382049637344</v>
       </c>
     </row>
-    <row r="122" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A122" s="5" t="s">
         <v>118</v>
       </c>
@@ -14368,7 +14368,7 @@
         <v>0.74172661870503598</v>
       </c>
     </row>
-    <row r="123" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
         <v>119</v>
       </c>
@@ -14471,7 +14471,7 @@
         <v>0.25507959104438982</v>
       </c>
     </row>
-    <row r="124" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A124" s="5" t="s">
         <v>120</v>
       </c>
@@ -14560,7 +14560,7 @@
         <v>0.33037400831129582</v>
       </c>
     </row>
-    <row r="125" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A125" s="5" t="s">
         <v>269</v>
       </c>
@@ -14651,7 +14651,7 @@
         <v>0.51533556027938054</v>
       </c>
     </row>
-    <row r="126" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A126" s="5" t="s">
         <v>121</v>
       </c>
@@ -14742,7 +14742,7 @@
         <v>0.38034566807001996</v>
       </c>
     </row>
-    <row r="127" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A127" s="5" t="s">
         <v>122</v>
       </c>
@@ -14883,7 +14883,7 @@
         <v>0.62094732291730992</v>
       </c>
     </row>
-    <row r="128" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A128" s="5" t="s">
         <v>123</v>
       </c>
@@ -15034,7 +15034,7 @@
         <v>0.87027729146665156</v>
       </c>
     </row>
-    <row r="129" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A129" s="5" t="s">
         <v>124</v>
       </c>
@@ -15187,7 +15187,7 @@
         <v>1.0265165543293091</v>
       </c>
     </row>
-    <row r="130" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A130" s="5" t="s">
         <v>125</v>
       </c>
@@ -15328,7 +15328,7 @@
         <v>1.0392343198479499</v>
       </c>
     </row>
-    <row r="131" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A131" s="5" t="s">
         <v>126</v>
       </c>
@@ -15442,7 +15442,7 @@
         <v>0.63011648032932599</v>
       </c>
     </row>
-    <row r="132" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A132" s="5" t="s">
         <v>127</v>
       </c>
@@ -15581,7 +15581,7 @@
         <v>1.0907364844608773</v>
       </c>
     </row>
-    <row r="133" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A133" s="5" t="s">
         <v>128</v>
       </c>
@@ -15709,7 +15709,7 @@
         <v>0.57450116610520874</v>
       </c>
     </row>
-    <row r="134" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A134" s="5" t="s">
         <v>129</v>
       </c>
@@ -15835,7 +15835,7 @@
         <v>0.66538412209824283</v>
       </c>
     </row>
-    <row r="135" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A135" s="5" t="s">
         <v>130</v>
       </c>
@@ -15988,7 +15988,7 @@
         <v>0.88844058906596746</v>
       </c>
     </row>
-    <row r="136" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A136" s="5" t="s">
         <v>131</v>
       </c>
@@ -16104,7 +16104,7 @@
         <v>0.65241190557646245</v>
       </c>
     </row>
-    <row r="137" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A137" s="5" t="s">
         <v>132</v>
       </c>
@@ -16245,7 +16245,7 @@
         <v>0.76739401496259352</v>
       </c>
     </row>
-    <row r="138" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A138" s="5" t="s">
         <v>133</v>
       </c>
@@ -16336,7 +16336,7 @@
         <v>0.53939188425454954</v>
       </c>
     </row>
-    <row r="139" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A139" s="5" t="s">
         <v>134</v>
       </c>
@@ -16437,7 +16437,7 @@
         <v>0.31197218082463979</v>
       </c>
     </row>
-    <row r="140" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A140" s="5" t="s">
         <v>135</v>
       </c>
@@ -16526,7 +16526,7 @@
         <v>0.76055883065493024</v>
       </c>
     </row>
-    <row r="141" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A141" s="5" t="s">
         <v>136</v>
       </c>
@@ -16640,7 +16640,7 @@
         <v>0.61659318637274552</v>
       </c>
     </row>
-    <row r="142" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A142" s="5" t="s">
         <v>137</v>
       </c>
@@ -16729,7 +16729,7 @@
         <v>0.65674418604651164</v>
       </c>
     </row>
-    <row r="143" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A143" s="5" t="s">
         <v>138</v>
       </c>
@@ -16820,7 +16820,7 @@
         <v>0.29498347852207873</v>
       </c>
     </row>
-    <row r="144" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A144" s="5" t="s">
         <v>139</v>
       </c>
@@ -16923,7 +16923,7 @@
         <v>0.32485202552079334</v>
       </c>
     </row>
-    <row r="145" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A145" s="5" t="s">
         <v>140</v>
       </c>
@@ -17062,7 +17062,7 @@
         <v>0.78916510318949329</v>
       </c>
     </row>
-    <row r="146" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A146" s="5" t="s">
         <v>141</v>
       </c>
@@ -17165,7 +17165,7 @@
         <v>0.35030512235714723</v>
       </c>
     </row>
-    <row r="147" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A147" s="5" t="s">
         <v>270</v>
       </c>
@@ -17266,7 +17266,7 @@
         <v>0.39479300042680321</v>
       </c>
     </row>
-    <row r="148" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A148" s="5" t="s">
         <v>142</v>
       </c>
@@ -17355,7 +17355,7 @@
         <v>0.63992869875222813</v>
       </c>
     </row>
-    <row r="149" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A149" s="5" t="s">
         <v>143</v>
       </c>
@@ -17444,7 +17444,7 @@
         <v>0.55851721094439544</v>
       </c>
     </row>
-    <row r="150" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A150" s="5" t="s">
         <v>144</v>
       </c>
@@ -17533,7 +17533,7 @@
         <v>0.41385355328808376</v>
       </c>
     </row>
-    <row r="151" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A151" s="5" t="s">
         <v>145</v>
       </c>
@@ -17624,7 +17624,7 @@
         <v>0.40628728227153427</v>
       </c>
     </row>
-    <row r="152" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A152" s="5" t="s">
         <v>146</v>
       </c>
@@ -17763,7 +17763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A153" s="5" t="s">
         <v>147</v>
       </c>
@@ -17904,7 +17904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A154" s="5" t="s">
         <v>148</v>
       </c>
@@ -18030,7 +18030,7 @@
         <v>0.62469613259668511</v>
       </c>
     </row>
-    <row r="155" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A155" s="5" t="s">
         <v>149</v>
       </c>
@@ -18171,7 +18171,7 @@
         <v>0.75872233497632158</v>
       </c>
     </row>
-    <row r="156" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A156" s="5" t="s">
         <v>150</v>
       </c>
@@ -18287,7 +18287,7 @@
         <v>0.76780808148495605</v>
       </c>
     </row>
-    <row r="157" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A157" s="5" t="s">
         <v>151</v>
       </c>
@@ -18403,7 +18403,7 @@
         <v>0.77634652606287113</v>
       </c>
     </row>
-    <row r="158" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A158" s="5" t="s">
         <v>152</v>
       </c>
@@ -18494,7 +18494,7 @@
         <v>0.22577137420144081</v>
       </c>
     </row>
-    <row r="159" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A159" s="5" t="s">
         <v>153</v>
       </c>
@@ -18585,7 +18585,7 @@
         <v>0.659493851873034</v>
       </c>
     </row>
-    <row r="160" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A160" s="5" t="s">
         <v>154</v>
       </c>
@@ -18674,7 +18674,7 @@
         <v>0.30622417524758966</v>
       </c>
     </row>
-    <row r="161" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A161" s="5" t="s">
         <v>155</v>
       </c>
@@ -18788,7 +18788,7 @@
         <v>0.85645867542419252</v>
       </c>
     </row>
-    <row r="162" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A162" s="5" t="s">
         <v>156</v>
       </c>
@@ -18879,7 +18879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A163" s="5" t="s">
         <v>157</v>
       </c>
@@ -18970,7 +18970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A164" s="5" t="s">
         <v>158</v>
       </c>
@@ -19059,7 +19059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A165" s="5" t="s">
         <v>159</v>
       </c>
@@ -19150,7 +19150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A166" s="5" t="s">
         <v>160</v>
       </c>
@@ -19253,7 +19253,7 @@
         <v>0.41179487179487179</v>
       </c>
     </row>
-    <row r="167" spans="1:48" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:48" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A167" s="5" t="s">
         <v>161</v>
       </c>
@@ -19353,22 +19353,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{023C39E0-1681-4D3E-A16C-52E1C75CE2BB}">
   <dimension ref="A1:N59"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.88671875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="13.77734375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="20.5546875" style="4" customWidth="1"/>
-    <col min="4" max="5" width="8.6640625" style="4"/>
-    <col min="6" max="6" width="9.44140625" style="4" customWidth="1"/>
-    <col min="7" max="7" width="8.6640625" style="4"/>
-    <col min="8" max="8" width="11.109375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.21875" style="4" customWidth="1"/>
-    <col min="10" max="13" width="8.6640625" style="4"/>
-    <col min="14" max="14" width="19.88671875" style="4" customWidth="1"/>
-    <col min="15" max="16384" width="8.6640625" style="4"/>
+    <col min="1" max="1" width="14.875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="12.125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="17.5" style="4" customWidth="1"/>
+    <col min="4" max="5" width="8.625" style="4"/>
+    <col min="6" max="6" width="9.5" style="4" customWidth="1"/>
+    <col min="7" max="7" width="8.625" style="4"/>
+    <col min="8" max="8" width="11.125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="12.5" style="4" customWidth="1"/>
+    <col min="10" max="13" width="8.625" style="4"/>
+    <col min="14" max="14" width="15.75" style="4" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>266</v>
       </c>
@@ -19412,7 +19412,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>204</v>
       </c>
@@ -19456,7 +19456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>205</v>
       </c>
@@ -19500,7 +19500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>206</v>
       </c>
@@ -19544,7 +19544,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>207</v>
       </c>
@@ -19588,7 +19588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>208</v>
       </c>
@@ -19632,7 +19632,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>209</v>
       </c>
@@ -19676,7 +19676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>210</v>
       </c>
@@ -19720,7 +19720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>211</v>
       </c>
@@ -19764,7 +19764,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
         <v>325</v>
       </c>
@@ -19808,7 +19808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
         <v>212</v>
       </c>
@@ -19852,7 +19852,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>213</v>
       </c>
@@ -19896,7 +19896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>214</v>
       </c>
@@ -19940,7 +19940,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>215</v>
       </c>
@@ -19984,7 +19984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
         <v>216</v>
       </c>
@@ -20028,7 +20028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>217</v>
       </c>
@@ -20072,7 +20072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>218</v>
       </c>
@@ -20116,7 +20116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>219</v>
       </c>
@@ -20160,7 +20160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
         <v>220</v>
       </c>
@@ -20188,14 +20188,11 @@
       <c r="I19" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="M19" s="4">
-        <v>70</v>
-      </c>
       <c r="N19" s="4" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>221</v>
       </c>
@@ -20239,7 +20236,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>222</v>
       </c>
@@ -20283,7 +20280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>223</v>
       </c>
@@ -20327,7 +20324,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
         <v>224</v>
       </c>
@@ -20371,7 +20368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>225</v>
       </c>
@@ -20415,7 +20412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>226</v>
       </c>
@@ -20459,7 +20456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>227</v>
       </c>
@@ -20503,7 +20500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
         <v>228</v>
       </c>
@@ -20547,7 +20544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>229</v>
       </c>
@@ -20591,7 +20588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>230</v>
       </c>
@@ -20635,7 +20632,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>231</v>
       </c>
@@ -20679,7 +20676,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
         <v>232</v>
       </c>
@@ -20723,7 +20720,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>233</v>
       </c>
@@ -20767,7 +20764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>234</v>
       </c>
@@ -20811,7 +20808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>235</v>
       </c>
@@ -20855,7 +20852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
         <v>236</v>
       </c>
@@ -20899,7 +20896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>237</v>
       </c>
@@ -20943,7 +20940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>238</v>
       </c>
@@ -20987,7 +20984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>239</v>
       </c>
@@ -21031,7 +21028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
         <v>240</v>
       </c>
@@ -21075,7 +21072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
         <v>241</v>
       </c>
@@ -21119,7 +21116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
         <v>242</v>
       </c>
@@ -21163,7 +21160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>243</v>
       </c>
@@ -21207,7 +21204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>244</v>
       </c>
@@ -21251,7 +21248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>245</v>
       </c>
@@ -21295,7 +21292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
         <v>246</v>
       </c>
@@ -21339,7 +21336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>247</v>
       </c>
@@ -21383,7 +21380,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>248</v>
       </c>
@@ -21415,7 +21412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>249</v>
       </c>
@@ -21459,7 +21456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
         <v>250</v>
       </c>
@@ -21503,7 +21500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>251</v>
       </c>
@@ -21547,7 +21544,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>252</v>
       </c>
@@ -21591,7 +21588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>253</v>
       </c>
@@ -21635,7 +21632,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
         <v>254</v>
       </c>
@@ -21679,7 +21676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
         <v>255</v>
       </c>
@@ -21723,7 +21720,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
         <v>256</v>
       </c>
@@ -21767,7 +21764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
         <v>257</v>
       </c>
@@ -21811,7 +21808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
         <v>258</v>
       </c>
@@ -21855,7 +21852,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
         <v>259</v>
       </c>
@@ -21899,7 +21896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
         <v>260</v>
       </c>
